--- a/TestCases.xlsx
+++ b/TestCases.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="TestCases.xlsx" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
-  <si>
-    <t>TC ID</t>
-  </si>
-  <si>
-    <t>Test Case</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
+  <si>
+    <t>Test Case ID</t>
+  </si>
+  <si>
+    <t>Scenario</t>
   </si>
   <si>
     <t>Steps</t>
@@ -31,92 +31,101 @@
     <t>TC01</t>
   </si>
   <si>
-    <t>Add product to cart</t>
-  </si>
-  <si>
-    <t>Select a product and click add to cart</t>
-  </si>
-  <si>
-    <t>Product added</t>
+    <t>Register with valid data</t>
+  </si>
+  <si>
+    <t>Fill all fields correctly → Continue</t>
+  </si>
+  <si>
+    <t>Account created</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>TC02</t>
+  </si>
+  <si>
+    <t>Empty fields</t>
+  </si>
+  <si>
+    <t>Click Continue empty</t>
+  </si>
+  <si>
+    <t>Error messages</t>
+  </si>
+  <si>
+    <t>TC03</t>
+  </si>
+  <si>
+    <t>Invalid email</t>
+  </si>
+  <si>
+    <t>enter wrong email</t>
+  </si>
+  <si>
+    <t>validation message</t>
+  </si>
+  <si>
+    <t>TC04</t>
+  </si>
+  <si>
+    <t>Short password</t>
+  </si>
+  <si>
+    <t>enter 123</t>
+  </si>
+  <si>
+    <t>password error</t>
   </si>
   <si>
     <t>pass</t>
   </si>
   <si>
-    <t>TC02</t>
-  </si>
-  <si>
-    <t>Add multiple products</t>
-  </si>
-  <si>
-    <t>Add 2 items</t>
-  </si>
-  <si>
-    <t>Both appear in cart</t>
-  </si>
-  <si>
-    <t>TC03</t>
-  </si>
-  <si>
-    <t>Update quantity</t>
-  </si>
-  <si>
-    <t>Change quantity to 2</t>
-  </si>
-  <si>
-    <t>Total updated</t>
-  </si>
-  <si>
-    <t>TC04</t>
-  </si>
-  <si>
-    <t>Remove product</t>
-  </si>
-  <si>
-    <t>Select the product and click remove</t>
-  </si>
-  <si>
-    <t>Product removed</t>
-  </si>
-  <si>
     <t>TC05</t>
   </si>
   <si>
-    <t>Empty cart</t>
-  </si>
-  <si>
-    <t>Remove all items</t>
-  </si>
-  <si>
-    <t>Same results as "iPhone"</t>
+    <t>Existing Email</t>
+  </si>
+  <si>
+    <t>enter chayma.ferhi@gmail.com</t>
+  </si>
+  <si>
+    <t>Email already registered message</t>
   </si>
   <si>
     <t>TC06</t>
   </si>
   <si>
-    <t>Cart total calculation</t>
-  </si>
-  <si>
-    <t>Add products</t>
-  </si>
-  <si>
-    <t>Total correct</t>
+    <t>Empty Username</t>
+  </si>
+  <si>
+    <t>put all the field except username</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>TC07</t>
+  </si>
+  <si>
+    <t>Privacy unchecked</t>
+  </si>
+  <si>
+    <t>don't check box</t>
+  </si>
+  <si>
+    <t>warning message</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -140,17 +149,11 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -370,9 +373,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="19.88"/>
-    <col customWidth="1" min="3" max="3" width="29.13"/>
-    <col customWidth="1" min="4" max="4" width="23.63"/>
+    <col customWidth="1" min="2" max="2" width="19.38"/>
+    <col customWidth="1" min="3" max="3" width="25.63"/>
+    <col customWidth="1" min="4" max="4" width="26.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -388,109 +391,126 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="C7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>9</v>
       </c>
     </row>
